--- a/SGC-CKN/Excel/104b5eba-1a28-4409-b344-aef283102f9a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-133_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/104b5eba-1a28-4409-b344-aef283102f9a_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-133_D800_10-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-133</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGC-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất san lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">10:45
@@ -106,10 +106,13 @@
 10/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">11:20
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">11:35
@@ -129,9 +132,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">12:00
 10/03/2026</t>
   </si>
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa xám vàng, xám xanh TT chặt lẫn sỏi san, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -159,9 +159,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">15:20
 10/03/2026</t>
   </si>
@@ -172,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:45
@@ -190,9 +187,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>Sỏi, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:40
@@ -233,7 +227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -309,11 +303,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -326,7 +315,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -401,11 +390,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -501,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -602,22 +586,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1218,24 +1193,24 @@
         <v>4.91</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-1.227</v>
@@ -1253,24 +1228,24 @@
         <v>19.5</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-7.727</v>
@@ -1288,21 +1263,21 @@
         <v>8</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>38</v>
@@ -1323,7 +1298,7 @@
         <v>19.68</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,7 +1333,7 @@
         <v>4.3</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1393,163 +1368,163 @@
         <v>4</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-26.227</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-36.227</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>1.33</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>10</v>
       </c>
       <c r="J17" s="12">
         <v>7.5</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-36.227</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-38.727</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>0.42</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>2.5</v>
       </c>
       <c r="J18" s="12">
         <v>6</v>
       </c>
-      <c r="K18" s="29" t="s">
-        <v>9</v>
+      <c r="K18" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
+      <c r="D19" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="31">
+      <c r="F19" s="28">
         <v>-38.727</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="28">
         <v>-40.227</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="28">
         <v>0.25</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="28">
         <v>1.5</v>
       </c>
       <c r="J19" s="12">
         <v>6</v>
       </c>
-      <c r="K19" s="32" t="s">
-        <v>9</v>
+      <c r="K19" s="29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="34">
+      <c r="F20" s="31">
         <v>-40.227</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="31">
         <v>-44.227</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="31">
         <v>1.67</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="31">
         <v>4</v>
       </c>
       <c r="J20" s="8">
         <v>2.4</v>
       </c>
-      <c r="K20" s="35" t="s">
-        <v>9</v>
+      <c r="K20" s="32" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="A23" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1631,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1644,31 +1619,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1708,7 +1683,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1737,7 +1712,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1766,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1827,22 +1802,22 @@
         <v>43</v>
       </c>
       <c r="D7" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="22">
         <v>-22.23</v>
       </c>
       <c r="F7" s="22">
-        <v>-26.23</v>
+        <v>-36.23</v>
       </c>
       <c r="G7" s="22">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="H7" s="22">
-        <v>4</v>
-      </c>
-      <c r="I7" s="8">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="I7" s="12">
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1853,25 +1828,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-26.23</v>
+        <v>-36.23</v>
       </c>
       <c r="F8" s="25">
-        <v>-36.23</v>
+        <v>-38.73</v>
       </c>
       <c r="G8" s="25">
-        <v>1.33</v>
+        <v>0.42</v>
       </c>
       <c r="H8" s="25">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I8" s="12">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1882,22 +1857,22 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-36.23</v>
+        <v>-38.73</v>
       </c>
       <c r="F9" s="28">
-        <v>-38.73</v>
+        <v>-40.23</v>
       </c>
       <c r="G9" s="28">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H9" s="28">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I9" s="12">
         <v>6</v>
@@ -1911,82 +1886,53 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-38.73</v>
+        <v>-40.23</v>
       </c>
       <c r="F10" s="31">
-        <v>-40.23</v>
+        <v>-44.23</v>
       </c>
       <c r="G10" s="31">
-        <v>0.25</v>
+        <v>1.67</v>
       </c>
       <c r="H10" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+        <v>4</v>
+      </c>
+      <c r="I10" s="8">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="36">
         <v>10</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-40.23</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="36">
         <v>-44.23</v>
       </c>
-      <c r="G11" s="34">
-        <v>1.67</v>
-      </c>
-      <c r="H11" s="34">
-        <v>4</v>
-      </c>
-      <c r="I11" s="8">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="39">
-        <v>10</v>
-      </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39">
-        <v>-44.23</v>
-      </c>
-      <c r="G12" s="39">
+      <c r="G11" s="36">
         <v>6.92</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H11" s="36">
         <v>44.23</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I11" s="36">
         <v>6.39</v>
       </c>
     </row>
